--- a/templates/test-demoqa.xlsx
+++ b/templates/test-demoqa.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,6 +415,9 @@
       <c r="E1" t="str">
         <v>permanentAddress</v>
       </c>
+      <c r="F1" t="str">
+        <v>저장버튼</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +435,9 @@
       <c r="E2" t="str">
         <v>서울시 서초구 반포대로 456</v>
       </c>
+      <c r="F2" t="str">
+        <v>Submit</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -449,6 +455,9 @@
       <c r="E3" t="str">
         <v>부산시 남구 대연동 77</v>
       </c>
+      <c r="F3" t="str">
+        <v>Submit</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -466,10 +475,13 @@
       <c r="E4" t="str">
         <v>대전시 서구 둔산동 456</v>
       </c>
+      <c r="F4" t="str">
+        <v>Submit</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>